--- a/tams-common-basicdata/src/main/resources/tpl/ComBondQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/ComBondQuotationInfo001.xlsx
@@ -1,33 +1,103 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="2436"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="债券行情导入模板" sheetId="1" r:id="rId1"/>
+    <sheet name="填写说明" sheetId="3" r:id="rId2"/>
+    <sheet name="数据字典" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+债券代码需要和维护的债券资产信息中债券代码一致</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+日期格式：20201020</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>资产代码</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+  <si>
+    <t>债券代码</t>
   </si>
   <si>
     <t>债券简称</t>
   </si>
   <si>
-    <t>估值日</t>
+    <t>估值来源</t>
+  </si>
+  <si>
+    <t>估值日期</t>
   </si>
   <si>
     <t>剩余期限</t>
   </si>
   <si>
+    <t>市价全价</t>
+  </si>
+  <si>
+    <t>市价净价</t>
+  </si>
+  <si>
     <t>市场久期</t>
   </si>
   <si>
@@ -35,71 +105,170 @@
   </si>
   <si>
     <t>基点价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>利差久期</t>
   </si>
   <si>
     <t>利差凸性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>利率久期</t>
   </si>
   <si>
     <t>利率凸性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>市场收益率%</t>
   </si>
   <si>
-    <t>市价全价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市价净价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>估值来源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>导入日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>1、</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>导入模板sheet页中字体为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>红色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段,非红色字体字段为非必填或者是条件必填</t>
+    </r>
+  </si>
+  <si>
+    <t>CBC：中债登</t>
+  </si>
+  <si>
+    <t>CSD：中证登</t>
+  </si>
+  <si>
+    <t>SCH：上清所</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -107,15 +276,123 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -131,7 +408,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -416,83 +693,672 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" customWidth="1"/>
-    <col min="12" max="12" width="18.21875" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="21.08984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" style="7" customWidth="1"/>
+    <col min="7" max="8" width="17.54296875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="19.6328125" style="7" customWidth="1"/>
+    <col min="10" max="15" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C29">
-      <formula1>"中债登,中证登,上清所"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F33:F1048576">
+      <formula1>"01 封闭式净值型,02 封闭式非净值型,03 开放式净值型,04 开放式非净值型"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>数据字典!$A$2:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C17 C18:C32</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tams-common-basicdata/src/main/resources/tpl/ComBondQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/ComBondQuotationInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpace3.0\tams-common-basicdata\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,6 +33,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -41,6 +42,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -55,6 +57,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -63,6 +66,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -75,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>债券代码</t>
   </si>
@@ -92,15 +96,6 @@
     <t>剩余期限</t>
   </si>
   <si>
-    <t>市价全价</t>
-  </si>
-  <si>
-    <t>市价净价</t>
-  </si>
-  <si>
-    <t>市场久期</t>
-  </si>
-  <si>
     <t>市场凸性</t>
   </si>
   <si>
@@ -117,9 +112,6 @@
   </si>
   <si>
     <t>利率凸性</t>
-  </si>
-  <si>
-    <t>市场收益率%</t>
   </si>
   <si>
     <t>1、</t>
@@ -129,6 +121,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>导入模板sheet页中字体为</t>
@@ -138,6 +131,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>红色</t>
@@ -146,6 +140,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>的是</t>
@@ -155,6 +150,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>必填</t>
@@ -163,6 +159,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>字段,非红色字体字段为非必填或者是条件必填</t>
@@ -176,6 +173,26 @@
   </si>
   <si>
     <t>SCH：上清所</t>
+  </si>
+  <si>
+    <t>估价全价</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>估价净价(推荐)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>估价净价(行权)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>估价收益率%</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>估价久期</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -195,16 +212,19 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -212,6 +232,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -220,6 +241,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -227,6 +249,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -234,22 +257,26 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -450,7 +477,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -485,7 +512,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -694,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08984375" style="5" customWidth="1"/>
@@ -706,9 +733,10 @@
     <col min="7" max="8" width="17.54296875" style="7" customWidth="1"/>
     <col min="9" max="9" width="19.6328125" style="7" customWidth="1"/>
     <col min="10" max="15" width="16.6328125" customWidth="1"/>
+    <col min="16" max="16" width="17.54296875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -725,37 +753,40 @@
         <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -771,8 +802,9 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="11"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="10"/>
@@ -788,8 +820,9 @@
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="14"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="10"/>
@@ -805,8 +838,9 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="14"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="10"/>
@@ -822,8 +856,9 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="14"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="10"/>
@@ -839,8 +874,9 @@
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="14"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="10"/>
@@ -856,8 +892,9 @@
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="14"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="10"/>
@@ -873,8 +910,9 @@
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="14"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="10"/>
@@ -890,8 +928,9 @@
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="14"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="10"/>
@@ -907,8 +946,9 @@
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="14"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="10"/>
@@ -924,8 +964,9 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="14"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="10"/>
@@ -941,8 +982,9 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="14"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="10"/>
@@ -958,8 +1000,9 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="17"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="10"/>
@@ -975,8 +1018,9 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="14"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="10"/>
@@ -992,8 +1036,9 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="10"/>
@@ -1009,8 +1054,9 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="14"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="10"/>
@@ -1026,8 +1072,9 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="14"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="10"/>
@@ -1043,8 +1090,9 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="14"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="10"/>
@@ -1060,8 +1108,9 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="14"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="10"/>
@@ -1077,8 +1126,9 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="14"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="10"/>
@@ -1094,8 +1144,9 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="14"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="10"/>
@@ -1111,8 +1162,9 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="14"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="10"/>
@@ -1128,8 +1180,9 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="14"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
@@ -1145,8 +1198,9 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="14"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="10"/>
@@ -1162,8 +1216,9 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="14"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
@@ -1179,8 +1234,9 @@
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="14"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="10"/>
@@ -1196,8 +1252,9 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
       <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="14"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="10"/>
@@ -1213,8 +1270,9 @@
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="14"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="10"/>
@@ -1230,8 +1288,9 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
       <c r="O29" s="10"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="14"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="10"/>
@@ -1247,8 +1306,9 @@
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
       <c r="O30" s="10"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="14"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="10"/>
@@ -1264,8 +1324,9 @@
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="14"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="10"/>
@@ -1281,6 +1342,7 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
+      <c r="P32" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1299,7 +1361,7 @@
           <x14:formula1>
             <xm:f>数据字典!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C17 C18:C32</xm:sqref>
+          <xm:sqref>C2:C32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1317,10 +1379,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1344,17 +1406,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/tams-common-basicdata/src/main/resources/tpl/ComBondQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/ComBondQuotationInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpace3.0\tams-common-basicdata\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code_copy\广州银行\tams\tams-common-basicdata\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>债券代码</t>
   </si>
@@ -180,10 +180,6 @@
   </si>
   <si>
     <t>估价净价(推荐)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>估价净价(行权)</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -721,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08984375" style="5" customWidth="1"/>
@@ -733,10 +729,9 @@
     <col min="7" max="8" width="17.54296875" style="7" customWidth="1"/>
     <col min="9" max="9" width="19.6328125" style="7" customWidth="1"/>
     <col min="10" max="15" width="16.6328125" customWidth="1"/>
-    <col min="16" max="16" width="17.54296875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -759,7 +754,7 @@
         <v>17</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>5</v>
@@ -780,13 +775,10 @@
         <v>10</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -802,9 +794,8 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="10"/>
@@ -820,9 +811,8 @@
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="10"/>
@@ -838,9 +828,8 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
-      <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="10"/>
@@ -856,9 +845,8 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
-      <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="10"/>
@@ -874,9 +862,8 @@
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
-      <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="10"/>
@@ -892,9 +879,8 @@
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
-      <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="10"/>
@@ -910,9 +896,8 @@
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
-      <c r="P8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="10"/>
@@ -928,9 +913,8 @@
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="10"/>
@@ -946,9 +930,8 @@
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
-      <c r="P10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="10"/>
@@ -964,9 +947,8 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
-      <c r="P11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="10"/>
@@ -982,9 +964,8 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
-      <c r="P12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="10"/>
@@ -1000,9 +981,8 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
-      <c r="P13" s="17"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="10"/>
@@ -1018,9 +998,8 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
-      <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="10"/>
@@ -1036,9 +1015,8 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
-      <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="10"/>
@@ -1054,9 +1032,8 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
-      <c r="P16" s="14"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="10"/>
@@ -1072,9 +1049,8 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
-      <c r="P17" s="14"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="10"/>
@@ -1090,9 +1066,8 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
-      <c r="P18" s="14"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="10"/>
@@ -1108,9 +1083,8 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
-      <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="10"/>
@@ -1126,9 +1100,8 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
-      <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="10"/>
@@ -1144,9 +1117,8 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
-      <c r="P21" s="14"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="10"/>
@@ -1162,9 +1134,8 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
-      <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="10"/>
@@ -1180,9 +1151,8 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
-      <c r="P23" s="14"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="10"/>
@@ -1198,9 +1168,8 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
-      <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="10"/>
@@ -1216,9 +1185,8 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
-      <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="10"/>
@@ -1234,9 +1202,8 @@
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
-      <c r="P26" s="14"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="10"/>
@@ -1252,9 +1219,8 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
       <c r="O27" s="10"/>
-      <c r="P27" s="14"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="10"/>
@@ -1270,9 +1236,8 @@
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
-      <c r="P28" s="14"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="10"/>
@@ -1288,9 +1253,8 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
       <c r="O29" s="10"/>
-      <c r="P29" s="14"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="10"/>
@@ -1306,9 +1270,8 @@
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
       <c r="O30" s="10"/>
-      <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="10"/>
@@ -1324,9 +1287,8 @@
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
-      <c r="P31" s="14"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="10"/>
@@ -1342,7 +1304,6 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
-      <c r="P32" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
